--- a/AAII_Financials/Yearly/BLSFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLSFY_YR_FIN.xlsx
@@ -653,148 +653,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11527200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10682800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11379300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12117700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13111400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9673300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7818400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8815800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8525400</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6956600</v>
+      </c>
+      <c r="E9" s="3">
         <v>6707300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6899300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7698800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7412000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5569900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4782400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5256100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4953000</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4570600</v>
+      </c>
+      <c r="E10" s="3">
         <v>3975400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4480000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4419000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5699400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4103400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3036000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3559700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3572300</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,38 +819,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E12" s="3">
         <v>19900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>18300</v>
       </c>
       <c r="K12" s="3">
         <v>18300</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3">
+        <v>18300</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -866,69 +882,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-75300</v>
+      </c>
+      <c r="E14" s="3">
         <v>295200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>23800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-50700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-26100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>129300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-170400</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>479300</v>
+      </c>
+      <c r="E15" s="3">
         <v>468000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>462300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>438100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>378600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>365700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>369100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>289700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>277600</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -938,68 +963,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10770000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10206300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10509500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11134100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10525000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8400600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7460900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7876400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7616100</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>757200</v>
+      </c>
+      <c r="E18" s="3">
         <v>476400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>869800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>983600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2586400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1272700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>357500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>939400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>909200</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1012,158 +1044,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8100</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1221000</v>
+      </c>
+      <c r="E21" s="3">
         <v>939700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1324400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1435100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2974400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1643300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>720200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1244700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1195000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E22" s="3">
         <v>34500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>37500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>39900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>44800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>32300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>63500</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>785800</v>
+      </c>
+      <c r="E23" s="3">
         <v>163200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>845500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>961300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2609000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1263800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>177000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>916900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1024300</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>164400</v>
+      </c>
+      <c r="E24" s="3">
         <v>45600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>213600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>234100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>555800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>291000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>88400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>205200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-199700</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1191,69 +1239,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>621400</v>
+      </c>
+      <c r="E26" s="3">
         <v>117600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>632000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>727300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2053200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>972800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>88600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>711800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1224000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>554800</v>
+      </c>
+      <c r="E27" s="3">
         <v>54900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>537600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>671700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1936100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>894700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>66600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>712200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1160600</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1281,39 +1338,45 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E29" s="3">
         <v>6300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>3900</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>2100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>7500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-3300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-3500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-19500</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1341,9 +1404,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1371,69 +1437,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8100</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>554800</v>
+      </c>
+      <c r="E33" s="3">
         <v>54900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>537600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>671700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1936100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>894700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>66600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>712200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1160600</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1461,74 +1536,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>554800</v>
+      </c>
+      <c r="E35" s="3">
         <v>54900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>537600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>671700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1936100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>894700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>66600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>712200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1160600</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1541,8 +1625,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1555,38 +1640,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>807300</v>
+      </c>
+      <c r="E41" s="3">
         <v>562300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>724200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>991500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1159400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1470900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>966200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1153100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>698500</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1614,219 +1703,243 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1311900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1232900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1135800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1270100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1499700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1229900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>760400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>858900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1075700</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2023700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2011500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2125800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2090500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2535100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1738000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1326700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1442200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1439300</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E45" s="3">
         <v>77000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>81700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>145500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>224300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>163700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>117700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>106800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>110300</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4232700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3883700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4067600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4497700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5418400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4602500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3171000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3560900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3323700</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E47" s="3">
         <v>83100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>98100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>112100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>117400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>102900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>72600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>80700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>53800</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>5590000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4845200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4328900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4012700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3916700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3658600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3116100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2908100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2995000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>1365300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1397400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1830900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1812400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1793100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1237300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1242700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1262000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1271300</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1854,9 +1967,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1884,39 +2000,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E52" s="3">
         <v>89400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>91500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>90200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>106400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>91700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>82800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>84500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>78300</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1944,39 +2066,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>11344800</v>
+      </c>
+      <c r="E54" s="3">
         <v>10346200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10460400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10605700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11444500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9858300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7981400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8201000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8085100</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1989,8 +2117,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2003,188 +2132,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1148300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1041400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1028800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1163100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1482200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1301300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>855000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1091500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1035700</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>126200</v>
+      </c>
+      <c r="E58" s="3">
         <v>95500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>127300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>114700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>491300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>126700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>150900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>148800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>70900</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>594300</v>
+      </c>
+      <c r="E59" s="3">
         <v>542200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>541000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>635400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>798600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>662200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>497400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>525000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>535000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2206400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1986100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2060300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2312400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3267900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2459900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1754300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2031300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1929100</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1096200</v>
+      </c>
+      <c r="E61" s="3">
         <v>485300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>354100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>408800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>415100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>745800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>760700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>518600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>580500</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E62" s="3">
         <v>168000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>163100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>169700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>153700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>185800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>179700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>155400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>153000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2212,9 +2360,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2242,9 +2393,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2272,39 +2426,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>3805700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2955700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2930700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3264200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4245800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3740100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3121200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3053400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2990700</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2317,8 +2477,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2346,9 +2507,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2376,9 +2540,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2406,9 +2573,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2436,39 +2606,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>5204800</v>
+      </c>
+      <c r="E72" s="3">
         <v>4961600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5167100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4761600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4379500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2899600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1791200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1891500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1367300</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2496,9 +2672,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2526,9 +2705,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2556,39 +2738,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>7132800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6993100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7153300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6966700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6740000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5720200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4517500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4812900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4729100</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2616,74 +2804,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>554800</v>
+      </c>
+      <c r="E81" s="3">
         <v>54900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>537600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>671700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1936100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>894700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>66600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>712200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1160600</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2696,38 +2893,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>433100</v>
+      </c>
+      <c r="E83" s="3">
         <v>414300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>407400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>384400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>343500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>330900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>332100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>254200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>239800</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2755,9 +2956,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2785,9 +2989,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2815,9 +3022,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2845,9 +3055,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2875,39 +3088,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1193800</v>
+      </c>
+      <c r="E89" s="3">
         <v>926300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>940800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1431500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1703200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1243200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>564700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1179600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>843700</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2920,38 +3139,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1015000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-797400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-642700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-531000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-513700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-564900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-387800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-254000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-292500</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2979,9 +3202,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3009,39 +3235,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-853800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-806300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-645200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-651600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1212500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-567900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-393700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-272200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-281400</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3054,38 +3286,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>591100</v>
+      </c>
+      <c r="E96" s="3">
         <v>172600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>150100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>155100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>237000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>52900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>49400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>53100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>45600</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3113,9 +3349,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3143,9 +3382,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3173,97 +3415,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-112800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-277800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-566600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-905600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-724500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-221800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-334000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-424900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-430100</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>9700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>36700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-32500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>9100</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>214200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-148100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-270500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-124100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-197100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>421100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-168400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>491100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>141300</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
